--- a/files/九龙-西南九龙-维港滙 III.xlsx
+++ b/files/九龙-西南九龙-维港滙 III.xlsx
@@ -15424,7 +15424,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
